--- a/data/Clinton.xlsx
+++ b/data/Clinton.xlsx
@@ -50302,7 +50302,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>This is a starting list, not proof. A parcel can be on here for innocent reasons: the credit is always one tax year behind, so a home that just sold may still show the previous owner's credit; two different people can share the same name; and a trust, LLC, or life estate can legally hold the credit when the right paperwork is on file. Before you contact anyone, look each parcel up on the county auditor's website and confirm it yourself. Everything here is public record from county auditor data. The list only includes parcels tied to a possible issue - the same name credited more than once, in more than one county, or a company-owned home.</t>
+          <t>This is a starting list, not proof. A parcel can be on here for innocent reasons: the credit is always one tax year behind, so a home that just sold may still show the previous owner's credit; two different people can share the same name; and a trust, LLC, or life estate can legally hold the credit when the right paperwork is on file. Before you contact anyone, look each parcel up on the county auditor's website and confirm it yourself. Everything here is public record from county auditor data. The list only includes parcels tied to a possible issue - the same name credited more than once, in more than one county, or a company-owned home. This file comes from an independent project that is not affiliated with the State of Ohio or any county auditor or tax agency, and nothing in it is legal or tax advice.</t>
         </is>
       </c>
     </row>
